--- a/0_1_Output_Data/5_ifoCAST_error_series_matched/ifoCAst_errors_filtered_T45.xlsx
+++ b/0_1_Output_Data/5_ifoCAST_error_series_matched/ifoCAst_errors_filtered_T45.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>Qminus1</t>
   </si>
@@ -92,6 +92,9 @@
   </si>
   <si>
     <t>2025-09-04_diff</t>
+  </si>
+  <si>
+    <t>2025-12-11_diff</t>
   </si>
 </sst>
 </file>
@@ -449,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -773,6 +776,14 @@
         <v>0.118688665</v>
       </c>
     </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25">
+        <v>-0.1443227</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
